--- a/POS_Mau_Test.xlsx
+++ b/POS_Mau_Test.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -440,7 +440,7 @@
         <v>HD0001</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-10T08:15:00Z</v>
+        <v>2026-05-11T01:15:00Z</v>
       </c>
       <c r="C2">
         <v>150000</v>
@@ -466,7 +466,7 @@
         <v>HD0001</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-10T08:15:00Z</v>
+        <v>2026-05-11T01:15:00Z</v>
       </c>
       <c r="C3">
         <v>150000</v>
@@ -492,7 +492,7 @@
         <v>HD0002</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-10T09:30:00Z</v>
+        <v>2026-05-11T02:30:00Z</v>
       </c>
       <c r="C4">
         <v>55000</v>
@@ -518,7 +518,7 @@
         <v>HD0003</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-10T12:05:00Z</v>
+        <v>2026-05-11T05:05:00Z</v>
       </c>
       <c r="C5">
         <v>210000</v>
@@ -539,9 +539,61 @@
         <v>Thẻ tín dụng</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>HD0004</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-11T07:20:00Z</v>
+      </c>
+      <c r="C6">
+        <v>320000</v>
+      </c>
+      <c r="D6">
+        <v>20000</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Nước ép trái cây</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>45000</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Chuyển khoản</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>HD0005</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-11T09:00:00Z</v>
+      </c>
+      <c r="C7">
+        <v>85000</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Bánh tiramisu</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>85000</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Tiền mặt</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/POS_Mau_Test.xlsx
+++ b/POS_Mau_Test.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H13"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -440,7 +440,7 @@
         <v>HD0001</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-11T01:15:00Z</v>
+        <v>2026-05-16T01:15:00.505Z</v>
       </c>
       <c r="C2">
         <v>150000</v>
@@ -466,7 +466,7 @@
         <v>HD0001</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-11T01:15:00Z</v>
+        <v>2026-05-16T01:15:00.505Z</v>
       </c>
       <c r="C3">
         <v>150000</v>
@@ -492,7 +492,7 @@
         <v>HD0002</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-11T02:30:00Z</v>
+        <v>2026-05-16T07:30:00.505Z</v>
       </c>
       <c r="C4">
         <v>55000</v>
@@ -518,7 +518,7 @@
         <v>HD0003</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-11T05:05:00Z</v>
+        <v>2026-05-15T02:00:00.505Z</v>
       </c>
       <c r="C5">
         <v>210000</v>
@@ -544,7 +544,7 @@
         <v>HD0004</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-11T07:20:00Z</v>
+        <v>2026-05-15T08:20:00.505Z</v>
       </c>
       <c r="C6">
         <v>320000</v>
@@ -567,33 +567,189 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>HD0004</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-15T08:20:00.505Z</v>
+      </c>
+      <c r="C7">
+        <v>320000</v>
+      </c>
+      <c r="D7">
+        <v>20000</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Bánh mì sandwich</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>50000</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Chuyển khoản</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
         <v>HD0005</v>
       </c>
-      <c r="B7" t="str">
-        <v>2026-05-11T09:00:00Z</v>
-      </c>
-      <c r="C7">
+      <c r="B8" t="str">
+        <v>2026-05-14T03:00:00.505Z</v>
+      </c>
+      <c r="C8">
         <v>85000</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>0</v>
       </c>
-      <c r="E7" t="str">
+      <c r="E8" t="str">
         <v>Bánh tiramisu</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <v>1</v>
       </c>
-      <c r="G7">
+      <c r="G8">
         <v>85000</v>
       </c>
-      <c r="H7" t="str">
+      <c r="H8" t="str">
         <v>Tiền mặt</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HD0006</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-14T09:45:00.505Z</v>
+      </c>
+      <c r="C9">
+        <v>120000</v>
+      </c>
+      <c r="D9">
+        <v>10000</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Sinh tố bơ</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>60000</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Chuyển khoản</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HD0007</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-13T04:30:00.505Z</v>
+      </c>
+      <c r="C10">
+        <v>95000</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Phở bò</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>95000</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Tiền mặt</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>HD0008</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-12T06:15:00.505Z</v>
+      </c>
+      <c r="C11">
+        <v>180000</v>
+      </c>
+      <c r="D11">
+        <v>15000</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Lẩu thái</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>90000</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Thẻ tín dụng</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>HD0009</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-11T05:00:00.505Z</v>
+      </c>
+      <c r="C12">
+        <v>75000</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Bún chả</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>75000</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Tiền mặt</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>HD0010</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-10T07:30:00.505Z</v>
+      </c>
+      <c r="C13">
+        <v>250000</v>
+      </c>
+      <c r="D13">
+        <v>25000</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Combo gia đình</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>250000</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Chuyển khoản</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
   </ignoredErrors>
 </worksheet>
 </file>